--- a/Sample_run/1/student/linhmndhe186854/TC1/GradeDetail.xlsx
+++ b/Sample_run/1/student/linhmndhe186854/TC1/GradeDetail.xlsx
@@ -1038,7 +1038,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="P2" s="0">
-        <x:v>39850</x:v>
+        <x:v>42884</x:v>
       </x:c>
       <x:c r="Q2" s="0">
         <x:v>4000</x:v>
@@ -1153,7 +1153,7 @@
         <x:v>4000</x:v>
       </x:c>
       <x:c r="Q4" s="0">
-        <x:v>39850</x:v>
+        <x:v>42884</x:v>
       </x:c>
       <x:c r="R4" s="4" t="s">
         <x:v>54</x:v>
